--- a/Тест2/098.xlsx
+++ b/Тест2/098.xlsx
@@ -267,7 +267,7 @@
     <t xml:space="preserve">Homiladorlik davrida faqat vitamin va temir qabul qilish</t>
   </si>
   <si>
-    <t xml:space="preserve">To'g'ri javob: Homiladorlikda tekshirish va tug'ishda antibiotik berish. Homiladorlikda B guruh streptokokk tekshiriladi va tug'ish paytida profilaktik antibiotik berilishi yangi tug'ilganlarda og'ir kasallik xavfini kamaytiradi. Manba: Mavzu materiali (098.docx); Riedel S. va boshq. Jawetz, Melnick &amp; Adelberg's Medical Microbiology, 28-nashr (2019); CDC. Guideline for Disinfection and Sterilization in Healthcare Facilities (2008).</t>
+    <t xml:space="preserve">To'g'ri javob: Homiladorlikda tekshirish va tug'ishda antibiotik berish. Homiladorlikda B guruh streptokokk tekshiriladi va tug'ish paytida profilaktik antibiotik berilishi yangi tug'ilganlarda og'ir kasallik xavfini kamaytiradi. Manba: Mavzu materiali (098.docx); Riedel S. va boshq. Jawetz, Melnick &amp; Adelberg's Medical Microbiology, 28-nashr (2019); CDC. Prevention of Perinatal Group B Streptococcal Disease: Revised Guidelines (MMWR 2010;59(RR-10)).</t>
   </si>
 </sst>
 </file>
